--- a/docs/templates/ir_excel_template_single_page.xlsx
+++ b/docs/templates/ir_excel_template_single_page.xlsx
@@ -818,7 +818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,30 +834,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>network_index</t>
+          <t>write_action</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>write_action</t>
+          <t>timer_instruction_kind</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>timer_instruction_kind</t>
+          <t>timer_preset_value</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>timer_preset_value</t>
+          <t>trigger_operands</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>trigger_operands</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -874,10 +869,7 @@
           <t>aux</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Consenso avvio</t>
         </is>
@@ -894,10 +886,7 @@
           <t>aux</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Ramo parallelo A</t>
         </is>
@@ -914,10 +903,7 @@
           <t>aux</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Ramo parallelo B</t>
         </is>
@@ -934,10 +920,7 @@
           <t>alarm</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Allarme temperatura</t>
         </is>
@@ -954,10 +937,7 @@
           <t>hmi</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Comando HMI</t>
         </is>
@@ -974,15 +954,12 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Uscita motore</t>
         </is>
@@ -999,25 +976,22 @@
           <t>timer</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>5</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>S5T#3S</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S5T#3S</t>
+          <t>M_OK_A</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>M_OK_A</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
         <is>
           <t>Timer fase</t>
         </is>
@@ -1034,10 +1008,7 @@
           <t>external</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Ingresso esterno</t>
         </is>
@@ -1054,10 +1025,7 @@
           <t>manual_mode</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Rete manuale</t>
         </is>
@@ -1074,10 +1042,7 @@
           <t>auto_mode</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Rete automatica</t>
         </is>
@@ -1094,14 +1059,7 @@
           <t>aux</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Fine ciclo</t>
         </is>

--- a/docs/templates/ir_excel_template_single_page.xlsx
+++ b/docs/templates/ir_excel_template_single_page.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,6 +523,11 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>parallel_group</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>jump_labels_used</t>
         </is>
       </c>
@@ -566,6 +571,7 @@
           <t>alternative</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -606,6 +612,11 @@
           <t>parallel</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -646,6 +657,11 @@
           <t>parallel</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -686,6 +702,11 @@
           <t>parallel</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -726,6 +747,11 @@
           <t>parallel</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -766,6 +792,7 @@
           <t>alternative</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -806,6 +833,7 @@
           <t>alternative</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
